--- a/АБК/Том СКС АБК/Журнал входного контроля СКС АБК.xlsx
+++ b/АБК/Том СКС АБК/Журнал входного контроля СКС АБК.xlsx
@@ -576,7 +576,7 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Рабочая документация 16/1/26-СКС-Р, лист 4; исполнительная документация 16/1/26-ИД-АБК, лист 5. Количество материалов — по АОСР № 1-СКС-АБК, 2-СКС-АБК, 3-СКС-АБК; оборудование — по исполнительной документации.</t>
+          <t>Рабочая документация 16/1/26-СКС-Р, лист 4; исполнительная документация 16/1/26-СКС-ИД-АБК, лист 2. Спецификация 16/1/26-СКС-ИД-АБК.СО. Количество материалов — по АОСР № 1-СКС-АБК, 2-СКС-АБК, 3-СКС-АБК; оборудование — по исполнительной документации.</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="K29" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 5</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 5</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 5</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K32" s="11" t="inlineStr">
         <is>
-          <t>ИД лист 5</t>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>

--- a/АБК/Том СКС АБК/Журнал входного контроля СКС АБК.xlsx
+++ b/АБК/Том СКС АБК/Журнал входного контроля СКС АБК.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1568,49 +1568,208 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>IP-телефон, Fanvil X301P</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Fanvil</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
+      <c r="A34" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Телефон проводной, TeXet TX-241</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>teXet</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>____________________ (подпись)</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>«____» ____________ 2026 г.</t>
+      <c r="A35" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Радиотелефон, Panasonic KX-TG6811RUB</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Panasonic</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Представитель лица, осуществляющего строительство</t>
+          <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
+          <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>____________________ (подпись)</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>«____» ____________ 2026 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Представитель лица, осуществляющего строительство</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -1618,15 +1777,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="I41:K41"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="I35:K35"/>
     <mergeCell ref="A37:K37"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="I38:K38"/>
@@ -1634,9 +1792,10 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G41:H41"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
